--- a/results/Int Task Remove ACC -0.9/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_7_permute.xlsx
@@ -440,477 +440,477 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6633459970377669</v>
+        <v>0.66427307652225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6851364111503759</v>
+        <v>0.6653774004983373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6854895184950087</v>
+        <v>0.6551522881513834</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6837539830666376</v>
+        <v>0.657756282113228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.686711084373115</v>
+        <v>0.6442495807713806</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.686225734479067</v>
+        <v>0.6260052407524956</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6847396835021301</v>
+        <v>0.6069088244861094</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6905066429182734</v>
+        <v>0.5944178248745472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6975265511458916</v>
+        <v>0.5797931805477921</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6956437725207087</v>
+        <v>0.6168830707430532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6991748459670365</v>
+        <v>0.6181196372685558</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6991748459670365</v>
+        <v>0.6198851739917197</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7074857967554389</v>
+        <v>0.6158401309951271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7227852728380909</v>
+        <v>0.6585047354675306</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7247580553476518</v>
+        <v>0.6588428421647672</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7151069151405482</v>
+        <v>0.660328893141704</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7063119960966737</v>
+        <v>0.6597943963897389</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7020160870100709</v>
+        <v>0.669740022990466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.685463662115944</v>
+        <v>0.6794197828537863</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6879054122335806</v>
+        <v>0.6876148733787458</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6891119774642906</v>
+        <v>0.6869250409754526</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6610623458486102</v>
+        <v>0.6717222795931193</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6477792725791324</v>
+        <v>0.6678230981547625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6477792725791324</v>
+        <v>0.6704570934113998</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.649779293106334</v>
+        <v>0.5893582644093061</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.649499807360107</v>
+        <v>0.6008077059115182</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6417286825010342</v>
+        <v>0.5999406290166207</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6401690099256916</v>
+        <v>0.6074431238611351</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6352555083956255</v>
+        <v>0.6528850192481992</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6616771750149217</v>
+        <v>0.6665239631394618</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6568372950832615</v>
+        <v>0.6705417681184136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6639703002971706</v>
+        <v>0.6208274515005384</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6314354751099784</v>
+        <v>0.5962749444976047</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6185013642694053</v>
+        <v>0.5943621645776291</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6194720640575014</v>
+        <v>0.5668034094103009</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6312132286761849</v>
+        <v>0.5258867751134523</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6312132286761849</v>
+        <v>0.489200520759317</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6131911350910935</v>
+        <v>0.4699529137573306</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6456864848904005</v>
+        <v>0.4642581943010172</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6464077002270624</v>
+        <v>0.4808964781637944</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6464077002270624</v>
+        <v>0.4234327481501833</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6376386375622527</v>
+        <v>0.4486206115211288</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.606851585173676</v>
+        <v>0.4665090809182291</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6166935888812044</v>
+        <v>0.4665090809182291</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.580514395884454</v>
+        <v>0.4696134254215182</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5841640928713765</v>
+        <v>0.4680061850037738</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5702128986619422</v>
+        <v>0.4694036137349086</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5835615010753096</v>
+        <v>0.4623578491282255</v>
       </c>
     </row>
     <row r="50">
@@ -920,407 +920,407 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5508316674719645</v>
+        <v>0.466892386934594</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5787666230858384</v>
+        <v>0.4661861722453285</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.597223538068485</v>
+        <v>0.4802668457270261</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5778095423065628</v>
+        <v>0.47929614593893</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5744693323606598</v>
+        <v>0.47929614593893</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5982323316058904</v>
+        <v>0.4800732189494494</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5951293687411773</v>
+        <v>0.4344609872636608</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.569033571448873</v>
+        <v>0.4367991144880989</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5831742475201561</v>
+        <v>0.411113663852861</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5878532652461843</v>
+        <v>0.3807750518706597</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.591501580594531</v>
+        <v>0.3491098694785775</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5771880023243108</v>
+        <v>0.3491098694785775</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.580290965189024</v>
+        <v>0.3636308909121341</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5847449732041068</v>
+        <v>0.3552735565429666</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5766112669073087</v>
+        <v>0.3504036753165137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5762581595626759</v>
+        <v>0.3504036753165137</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5838970418723335</v>
+        <v>0.3504036753165137</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5850230773117577</v>
+        <v>0.3432979081202452</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4762822000738979</v>
+        <v>0.3503614366514766</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4805044875620948</v>
+        <v>0.3546109621573142</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4909640837130866</v>
+        <v>0.359011678398752</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.486371122332648</v>
+        <v>0.359011678398752</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4865606041944968</v>
+        <v>0.3655270911691978</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4768917000628448</v>
+        <v>0.3466256833189643</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4668315948372509</v>
+        <v>0.3505398654047175</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4340159022652557</v>
+        <v>0.342552020666155</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5121876312556647</v>
+        <v>0.3745647838485661</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5194420232873209</v>
+        <v>0.5049188307074305</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5038944443918106</v>
+        <v>0.5182088121697883</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5485669644689929</v>
+        <v>0.5065304134178422</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5485669644689929</v>
+        <v>0.5078692211979675</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5487878292642103</v>
+        <v>0.503822796562799</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5428096765228815</v>
+        <v>0.5025589920196556</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5395336140822919</v>
+        <v>0.5007784546490954</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5387537777946205</v>
+        <v>0.5007784546490954</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4819775116610295</v>
+        <v>0.5004989689028685</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5190075966436446</v>
+        <v>0.5002931047550473</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5121935525638475</v>
+        <v>0.4969528948091443</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5144294385336631</v>
+        <v>0.4981594600398543</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4517819979599119</v>
+        <v>0.4977927336864012</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5085683303174137</v>
+        <v>0.4997791352047825</v>
       </c>
     </row>
   </sheetData>
